--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שני בן משה - שירים לא שלי</v>
+        <v>משה לוק - מתי יבוא גואלי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410900&amp;sid=e8f61624910ad71cfefc2731eed11f18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410921&amp;sid=46ded035bf04ed44d864fc936f252157</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,772 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שני בן משה - שירים לא שלי</v>
+        <v>משה לוק - מתי יבוא גואלי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410920&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410919&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ישראל זאודה - מה בליבו של גבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410918&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ישראל זאודה - מה בליבו של גבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יניב בן ישי - קשה בלב</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410917&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יניב בן ישי - קשה בלב</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אילון אלקיים - הנסיך שלי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410916&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אילון אלקיים - הנסיך שלי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410915&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>רז ארגס - טיול של שבת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410914&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>רז ארגס - טיול של שבת</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>רועי קורנבלום - גבר גבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410913&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>רועי קורנבלום - גבר גבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>רועי בנטין - איפה את</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410912&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>רועי בנטין - איפה את</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>מידד טסה - עליי תשמור</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410911&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>מידד טסה - עליי תשמור</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>מאיה בוסקילה - קח אותי לרקוד</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410910&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>מאיה בוסקילה - קח אותי לרקוד</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>מאור אדרי - פלה מראדונה</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410909&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>מאור אדרי - פלה מראדונה</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>יהונתן פתחיה - המבט שלך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410908&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>יהונתן פתחיה - המבט שלך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>טל ועקנין - פאפאוטה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410907&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>טל ועקנין - פאפאוטה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>טינה איב - סימנים</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410906&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>טינה איב - סימנים</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>הדר זעפרני - הדרך לי בית</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410905&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>הדר זעפרני - הדרך לי בית</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>בן ארצי - ישראל</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410904&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>בן ארצי - ישראל</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אמנון בן ש''ך - ים התמימות</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410903&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אמנון בן ש''ך - ים התמימות</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>אלישיב-ציון אביאל - תרקוד</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410902&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>אלישיב-ציון אביאל - תרקוד</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>אורצ'וק הקטן - אוהב כל רגע</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410901&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>אורצ'וק הקטן - אוהב כל רגע</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה לוק - מתי יבוא גואלי</v>
+        <v>שמעון שובייב - סיפור בלי התחלה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410921&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410928&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה לוק - מתי יבוא גואלי</v>
+        <v>שמעון שובייב - סיפור בלי התחלה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+        <v>רזיאל חי - תפילת הילדים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410920&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410927&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסת היוצר</v>
+        <v>רזיאל חי - תפילת הילדים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+        <v>עידו כנפי - הלב מושך הביתה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410919&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410926&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>כפיר עזרן - עיניים עצובות - גרסה מהירה</v>
+        <v>עידו כנפי - הלב מושך הביתה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל זאודה - מה בליבו של גבר</v>
+        <v>עומרי גורן - ויהי נעם</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410918&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410925&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ישראל זאודה - מה בליבו של גבר</v>
+        <v>עומרי גורן - ויהי נעם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יניב בן ישי - קשה בלב</v>
+        <v>עדן ג'לח - תורי לזרוח</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410917&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410924&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-17</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יניב בן ישי - קשה בלב</v>
+        <v>עדן ג'לח - תורי לזרוח</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אילון אלקיים - הנסיך שלי</v>
+        <v>נויה אוזן - טיפוטה</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410916&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410923&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-17</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אילון אלקיים - הנסיך שלי</v>
+        <v>נויה אוזן - טיפוטה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
+        <v>נהוראי אביסרור - שוהם</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410915&amp;sid=46ded035bf04ed44d864fc936f252157</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410922&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-17</v>
@@ -697,544 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אייל לוי &amp; סטפן לגר - חצופה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>רז ארגס - טיול של שבת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410914&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>רז ארגס - טיול של שבת</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>רועי קורנבלום - גבר גבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410913&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>רועי קורנבלום - גבר גבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>רועי בנטין - איפה את</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410912&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>רועי בנטין - איפה את</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>מידד טסה - עליי תשמור</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410911&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>מידד טסה - עליי תשמור</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>מאיה בוסקילה - קח אותי לרקוד</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410910&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>מאיה בוסקילה - קח אותי לרקוד</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>מאור אדרי - פלה מראדונה</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410909&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>מאור אדרי - פלה מראדונה</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>יהונתן פתחיה - המבט שלך</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410908&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>יהונתן פתחיה - המבט שלך</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>טל ועקנין - פאפאוטה</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410907&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>טל ועקנין - פאפאוטה</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>טינה איב - סימנים</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410906&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v>טינה איב - סימנים</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>הדר זעפרני - הדרך לי בית</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410905&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v>הדר זעפרני - הדרך לי בית</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>בן ארצי - ישראל</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410904&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D19" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v>בן ארצי - ישראל</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>אמנון בן ש''ך - ים התמימות</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410903&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D20" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v>אמנון בן ש''ך - ים התמימות</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>אלישיב-ציון אביאל - תרקוד</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410902&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D21" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v>אלישיב-ציון אביאל - תרקוד</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>אורצ'וק הקטן - אוהב כל רגע</v>
-      </c>
-      <c r="B22" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410901&amp;sid=46ded035bf04ed44d864fc936f252157</v>
-      </c>
-      <c r="D22" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v>אורצ'וק הקטן - אוהב כל רגע</v>
+        <v>נהוראי אביסרור - שוהם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון שובייב - סיפור בלי התחלה</v>
+        <v>מני חן - אחת ממליון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410928&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410938&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון שובייב - סיפור בלי התחלה</v>
+        <v>מני חן - אחת ממליון</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רזיאל חי - תפילת הילדים</v>
+        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410927&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410937&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רזיאל חי - תפילת הילדים</v>
+        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עידו כנפי - הלב מושך הביתה</v>
+        <v>נוימן - דדליין</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410926&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410936&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עידו כנפי - הלב מושך הביתה</v>
+        <v>נוימן - דדליין</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עומרי גורן - ויהי נעם</v>
+        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410925&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410935&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עומרי גורן - ויהי נעם</v>
+        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עדן ג'לח - תורי לזרוח</v>
+        <v>רונה גולד - לטובה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410924&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410934&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-17</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עדן ג'לח - תורי לזרוח</v>
+        <v>רונה גולד - לטובה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נויה אוזן - טיפוטה</v>
+        <v>דולב הרץ - לחזור</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410923&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410933&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-17</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נויה אוזן - טיפוטה</v>
+        <v>דולב הרץ - לחזור</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נהוראי אביסרור - שוהם</v>
+        <v>דולב הרץ - גיבור</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-17</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410922&amp;sid=6f4c51f9f2fa5edd8bf63762818ab696</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410932&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-17</v>
@@ -697,12 +697,126 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נהוראי אביסרור - שוהם</v>
+        <v>דולב הרץ - גיבור</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דולב הרץ - בן אדם</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410931&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דולב הרץ - בן אדם</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410930&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אוריאל גבאי - מתיקות התורה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410929&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-17</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אוריאל גבאי - מתיקות התורה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מני חן - אחת ממליון</v>
+        <v>עופרי שגיב - שוב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410938&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410945&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מני חן - אחת ממליון</v>
+        <v>עופרי שגיב - שוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
+        <v>עופר סופר - ירושלים</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410937&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410944&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל קהניאל מארח את קלייב ג׳ין - אורך ימים</v>
+        <v>עופר סופר - ירושלים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוימן - דדליין</v>
+        <v>ניצן פלד - פחדים</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410936&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410943&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוימן - דדליין</v>
+        <v>ניצן פלד - פחדים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
+        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410935&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410942&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נאוריאל דרהם - בני יהודה החלום הכתום 2026</v>
+        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רונה גולד - לטובה</v>
+        <v>מיה סולימן - לב שבור ואלכוהול</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410934&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410941&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רונה גולד - לטובה</v>
+        <v>מיה סולימן - לב שבור ואלכוהול</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דולב הרץ - לחזור</v>
+        <v>גלילי - אני עשיר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410933&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410940&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דולב הרץ - לחזור</v>
+        <v>גלילי - אני עשיר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דולב הרץ - גיבור</v>
+        <v>אופירה שופן - אין ידידות</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410932&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410939&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-17</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,126 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דולב הרץ - גיבור</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דולב הרץ - בן אדם</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410931&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דולב הרץ - בן אדם</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410930&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אלי הרצליך - מחרוזת סיום הש''ס 2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אוריאל גבאי - מתיקות התורה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410929&amp;sid=f96531229bdba7268ac0be5ce6cd0ad5</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אוריאל גבאי - מתיקות התורה</v>
+        <v>אופירה שופן - אין ידידות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עופרי שגיב - שוב</v>
+        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410945&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410957&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עופרי שגיב - שוב</v>
+        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עופר סופר - ירושלים</v>
+        <v>ינון אליה - הילד שהייתי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410944&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410956&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עופר סופר - ירושלים</v>
+        <v>ינון אליה - הילד שהייתי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ניצן פלד - פחדים</v>
+        <v>יוני מאמוש - עשן מהלב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410943&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410955&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ניצן פלד - פחדים</v>
+        <v>יוני מאמוש - עשן מהלב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
+        <v>טל גירטלר - חוזרת אלייך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410942&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410948&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מיקה משה &amp; אלי חולי - כמו פעם</v>
+        <v>טל גירטלר - חוזרת אלייך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מיה סולימן - לב שבור ואלכוהול</v>
+        <v>דורון רוקח - מחרוזת געגועים 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410941&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410947&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-19</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מיה סולימן - לב שבור ואלכוהול</v>
+        <v>דורון רוקח - מחרוזת געגועים 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>גלילי - אני עשיר</v>
+        <v>רון קטן - חיים חדשים</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410940&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410946&amp;sid=d5a00c8429477199f3ccba812a262145</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-19</v>
@@ -659,50 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>גלילי - אני עשיר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אופירה שופן - אין ידידות</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410939&amp;sid=72a8d6bd8af5c63a49266dfa26782102</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אופירה שופן - אין ידידות</v>
+        <v>רון קטן - חיים חדשים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
+        <v>שלומית אהרון - פיסות אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410957&amp;sid=d5a00c8429477199f3ccba812a262145</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410969&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יניב גליסקו - מחרוזת בית"ר ירושלים 2026</v>
+        <v>שלומית אהרון - פיסות אהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ינון אליה - הילד שהייתי</v>
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט - איך שהיא רוקדת</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410956&amp;sid=d5a00c8429477199f3ccba812a262145</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410968&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ינון אליה - הילד שהייתי</v>
+        <v>עדן חסון &amp; אופק אדנק מארחים את אגם בוחבוט - איך שהיא רוקדת</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יוני מאמוש - עשן מהלב</v>
+        <v>עדן בן זקן &amp; נועה קירל - אני משקרת</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410955&amp;sid=d5a00c8429477199f3ccba812a262145</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410967&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יוני מאמוש - עשן מהלב</v>
+        <v>עדן בן זקן &amp; נועה קירל - אני משקרת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טל גירטלר - חוזרת אלייך</v>
+        <v>נתנאל ששון - סטלה עבאד</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410948&amp;sid=d5a00c8429477199f3ccba812a262145</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410966&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טל גירטלר - חוזרת אלייך</v>
+        <v>נתנאל ששון - סטלה עבאד</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>דורון רוקח - מחרוזת געגועים 2026</v>
+        <v>נוריאל חדד - יורד הליל</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410947&amp;sid=d5a00c8429477199f3ccba812a262145</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410965&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>דורון רוקח - מחרוזת געגועים 2026</v>
+        <v>נוריאל חדד - יורד הליל</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>רון קטן - חיים חדשים</v>
+        <v>נויה גליק - זמן</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410946&amp;sid=d5a00c8429477199f3ccba812a262145</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410964&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,126 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>רון קטן - חיים חדשים</v>
+        <v>נויה גליק - זמן</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אסתר שמיר &amp; יהל דורון - בצד השני של הפחד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410963&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אסתר שמיר &amp; יהל דורון - בצד השני של הפחד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>החצר האחורית של ג'וני - טרף קל</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410962&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>החצר האחורית של ג'וני - טרף קל</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אורי כלטוב - לא רוצה לאהוב אותי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410961&amp;sid=891ed0add7d2bad4f73efc261e804606</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אורי כלטוב - לא רוצה לאהוב אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>